--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.4维保SLA.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.4维保SLA.xlsx
@@ -413,51 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>问题等级</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>问题等级</t>
+          <t>服务覆盖时间</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>服务覆盖时间</t>
+          <t>响应时间</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>响应时间</t>
+          <t>回复时间</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>回复时间</t>
+          <t>解决时间</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>解决时间</t>
+          <t>服务细项</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>服务细项</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>预案版本号</t>
         </is>
@@ -466,17 +461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7×24×365</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7×24×365</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,35 +486,30 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>热线受理</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>热线受理</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7×24×365</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7×24×365</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -534,40 +524,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>在线技术支持</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>在线技术支持</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>紧急问题</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>紧急问题</t>
+          <t>7×24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7×24</t>
+          <t>1 小时</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1 小时</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,40 +562,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>远程问题处理（单域）</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>远程问题处理（单域）</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>重要问题</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>重要问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>2 小时</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2 小时</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -620,40 +600,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>远程问题处理（单域）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>远程问题处理（单域）</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>一般问题</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>一般问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>4 小时</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4 小时</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -663,40 +638,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>远程问题处理（单域）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>远程问题处理（单域）</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>技术咨询</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>技术咨询</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>8 小时</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8 小时</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -706,40 +676,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>远程问题处理（单域）</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>远程问题处理（单域）</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>紧急问题</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>紧急问题</t>
+          <t>7×10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7×10</t>
+          <t>NBD人员到达</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NBD人员到达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -749,40 +714,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场问题处理</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>现场问题处理</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>重要问题</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>重要问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD人员到达</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NBD人员到达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,40 +752,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场问题处理</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>现场问题处理</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>一般问题</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一般问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD人员到达</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NBD人员到达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -835,40 +790,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场问题处理</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>现场问题处理</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>紧急问题</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>紧急问题</t>
+          <t>7×10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7×10</t>
+          <t>NBD备件送达</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NBD备件送达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -878,40 +828,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>备件先行</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>备件先行</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>重要问题</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>重要问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD备件送达</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NBD备件送达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -921,40 +866,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>备件先行</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>备件先行</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>一般问题</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>一般问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD备件送达</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NBD备件送达</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -964,40 +904,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>备件先行</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>备件先行</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>紧急问题</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>紧急问题</t>
+          <t>7×10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7×10</t>
+          <t>NBD完成更换</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NBD完成更换</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1007,40 +942,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场硬件更换</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>现场硬件更换</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>重要问题</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>重要问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD完成更换</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NBD完成更换</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1050,40 +980,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场硬件更换</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>现场硬件更换</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>一般问题</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>一般问题</t>
+          <t>5×8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5×8</t>
+          <t>NBD完成更换</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NBD完成更换</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1093,35 +1018,30 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>现场硬件更换</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>现场硬件更换</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>提供</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>提供</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1136,20 +1056,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>软件更新授权</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>软件更新授权</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
